--- a/lessons/qr/excels/remarks_minimal.xlsx
+++ b/lessons/qr/excels/remarks_minimal.xlsx
@@ -2307,6 +2307,11 @@
           <t>+sqrcode (00:00:00), -qrcode (13:05:55.667)</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="M30" t="n">
         <v>99.5</v>
       </c>
@@ -2375,7 +2380,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Q, Q</t>
+          <t>Q, Q, H</t>
         </is>
       </c>
       <c r="M31" t="n">
